--- a/xiuxian配置表/yunxing_params/境界突破.xlsx
+++ b/xiuxian配置表/yunxing_params/境界突破.xlsx
@@ -968,17 +968,17 @@
     <row r="5" ht="27" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>qi_to_foundation</t>
+          <t>lianqi_to_zhuji</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1001,17 +1001,17 @@
     <row r="6" ht="27" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>foundation_to_core</t>
+          <t>zhuji_to_jindan</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>jindan</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1034,17 +1034,17 @@
     <row r="7" ht="27" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>core_to_nascent</t>
+          <t>jindan_to_yuanying</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>jindan</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>nascent</t>
+          <t>yuanying</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">

--- a/xiuxian配置表/yunxing_params/境界突破.xlsx
+++ b/xiuxian配置表/yunxing_params/境界突破.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="z_tupo_rules" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="z_tupo_rules_component_caps" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="z_tupo_rules_major_breakthrough" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="说明" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="z_tupo_rules" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="z_tupo_rules_component_caps" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="z_tupo_rules_major_breakthrough" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.25" customWidth="1" min="1" max="1"/>
@@ -674,18 +674,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>realm_unstable_cultivation_multiplier</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-    </row>
+    <row r="13" ht="27" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
